--- a/artfynd/A 4720-2022 artfynd.xlsx
+++ b/artfynd/A 4720-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4720-2022 artfynd.xlsx
+++ b/artfynd/A 4720-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102649157</v>
+        <v>102649116</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,6 +718,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>i vatten/simmande</t>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SV Ljungby bergtäkt, Hl</t>
+          <t>Sedimenteringsdamm SV om Ljungby bergtäkt, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352200.8870156127</v>
+        <v>352198</v>
       </c>
       <c r="R2" t="n">
-        <v>6319448.62230575</v>
+        <v>6319478</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,22 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102649161</v>
+        <v>102649119</v>
       </c>
       <c r="B3" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -856,7 +841,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -866,14 +851,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Ljungby bergtäkt, Hl</t>
+          <t>Sedimenteringsdamm SV om Ljungby bergtäkt, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352199.7958508753</v>
+        <v>352197</v>
       </c>
       <c r="R3" t="n">
-        <v>6319448.661186199</v>
+        <v>6319477</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,22 +885,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,6 +914,727 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102649121</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sedimenteringsdamm SV om Ljungby bergtäkt, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>352199</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6319474</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102649168</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sedimenteringsdamm SV om Ljungby bergtäkt, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>352190</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6319475</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102649157</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SV Ljungby bergtäkt, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>352201</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6319448</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102649167</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sedimenteringsdamm SV om Ljungby bergtäkt, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>352190</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6319475</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102649162</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sedimenteringsdamm SV om Ljungby bergtäkt, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>352199</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6319472</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102649118</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SV Ljungby bergtäkt, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>352200</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6319448</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4720-2022 artfynd.xlsx
+++ b/artfynd/A 4720-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649116</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649121</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649157</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649167</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1514,6 +1549,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649162</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1635,8 +1675,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102649118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>